--- a/output/pdf_financials_xlsx/WMK.xlsx
+++ b/output/pdf_financials_xlsx/WMK.xlsx
@@ -2176,25 +2176,25 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.066118</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.052266</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.333651</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.80821</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.010064</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.570689</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.03901</v>
       </c>
     </row>
     <row r="35">
@@ -2250,25 +2250,25 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.066118</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.052266</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.333651</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.80821</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.010064</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.570689</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.03901</v>
       </c>
     </row>
     <row r="37">
@@ -2694,25 +2694,25 @@
         <v>4.726584</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>13.187175</v>
+        <v>13.121057</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.915084</v>
+        <v>8.862818000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.846595</v>
+        <v>0.512944</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.701508</v>
+        <v>0.893298</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.619938</v>
+        <v>0.609874</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.060925</v>
+        <v>0.490236</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.923887</v>
+        <v>1.884877</v>
       </c>
     </row>
     <row r="49">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/WMK.xlsx
+++ b/output/pdf_financials_xlsx/WMK.xlsx
@@ -4637,10 +4637,8 @@
       <c r="F100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -4676,10 +4674,8 @@
       <c r="F101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>0</v>
@@ -4715,10 +4711,8 @@
       <c r="F102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H102" s="3" t="n">
         <v>0</v>
@@ -4754,10 +4748,8 @@
       <c r="F103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>0</v>
@@ -4793,10 +4785,8 @@
       <c r="F104" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H104" s="3" t="n">
         <v>0</v>
@@ -4832,10 +4822,8 @@
       <c r="F105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H105" s="3" t="n">
         <v>0</v>
@@ -4871,10 +4859,8 @@
       <c r="F106" s="3" t="n">
         <v>-1.317615</v>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0</v>
@@ -4910,10 +4896,8 @@
       <c r="F107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H107" s="3" t="n">
         <v>0</v>
@@ -4949,10 +4933,8 @@
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -4988,10 +4970,8 @@
       <c r="F109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H109" s="3" t="n">
         <v>0</v>
@@ -5027,10 +5007,8 @@
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
@@ -5066,10 +5044,8 @@
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G111" s="3" t="n">
+        <v>-0.005715</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -5105,10 +5081,8 @@
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -5144,10 +5118,8 @@
       <c r="F113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H113" s="3" t="n">
         <v>0</v>
@@ -5183,10 +5155,8 @@
       <c r="F114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
@@ -5222,10 +5192,8 @@
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -5261,10 +5229,8 @@
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -5300,10 +5266,8 @@
       <c r="F117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
         <v>0</v>
@@ -5339,10 +5303,8 @@
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -5380,10 +5342,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G119" s="3" t="n">
+        <v>-0.005715</v>
       </c>
       <c r="H119" s="1" t="inlineStr">
         <is>
@@ -5421,10 +5381,8 @@
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -5460,10 +5418,8 @@
       <c r="F121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -5499,10 +5455,8 @@
       <c r="F122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H122" s="3" t="n">
         <v>0</v>
@@ -5538,10 +5492,8 @@
       <c r="F123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H123" s="3" t="n">
         <v>0</v>
@@ -5577,10 +5529,8 @@
       <c r="F124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -5616,10 +5566,8 @@
       <c r="F125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -5655,10 +5603,8 @@
       <c r="F126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>0</v>
@@ -5751,10 +5697,8 @@
       <c r="F128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
@@ -5794,10 +5738,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H129" s="1" t="inlineStr">
         <is>
@@ -5835,10 +5777,8 @@
       <c r="F130" s="3" t="n">
         <v>0.066118</v>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="3" t="n">
+        <v>3.64744</v>
       </c>
       <c r="H130" s="3" t="n">
         <v>2.333651</v>
@@ -5874,10 +5814,8 @@
       <c r="F131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H131" s="3" t="n">
         <v>0</v>
@@ -5913,10 +5851,8 @@
       <c r="F132" s="3" t="n">
         <v>-0.013852</v>
       </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="3" t="n">
+        <v>-1.313789</v>
       </c>
       <c r="H132" s="3" t="n">
         <v>-0.525441</v>
@@ -5952,10 +5888,8 @@
       <c r="F133" s="3" t="n">
         <v>0.052266</v>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="3" t="n">
+        <v>2.333651</v>
       </c>
       <c r="H133" s="3" t="n">
         <v>1.80821</v>
@@ -5991,10 +5925,8 @@
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G134" s="3" t="n">
+        <v>-0.005715</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -6032,10 +5964,8 @@
       <c r="F135" s="3" t="n">
         <v>-0.013852</v>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="3" t="n">
+        <v>-1.313789</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.525441</v>
@@ -6061,7 +5991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:N189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14348,10 +14278,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J133" s="5" t="n">
+        <v>-0.568376</v>
       </c>
       <c r="K133" s="5" t="n">
         <v>-0.33758</v>
@@ -14474,10 +14402,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J135" s="5" t="n">
+        <v>-1.308074</v>
       </c>
       <c r="K135" s="5" t="n">
         <v>-0.525441</v>
@@ -15002,10 +14928,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J143" s="5" t="n">
+        <v>-0.005715</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -15896,12 +15820,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) $</t>
+          <t>Depreciation [note 6]</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -15920,21 +15844,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H157" s="5" t="n">
-        <v>-0.408696</v>
-      </c>
-      <c r="I157" s="5" t="n">
-        <v>13.495571</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>0.013362</v>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>0.005713</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -15965,38 +15889,40 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>0.034507</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>0.658626</v>
-      </c>
-      <c r="G158" s="5" t="n">
-        <v>1.594738</v>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>1.201926</v>
-      </c>
-      <c r="I158" s="5" t="n">
-        <v>0.8601259999999999</v>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in asset retirement obligations [note 8]</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>1.539956</v>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>-0.321074</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -16027,7 +15953,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Impairment</t>
+          <t>Accretion of asset retirement obligations [note 8]</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -16036,8 +15962,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F159" s="5" t="n">
-        <v>4.5</v>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -16049,18 +15977,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="5" t="n">
-        <v>3.010705</v>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="n">
+        <v>0.012285</v>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>0.014133</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -16091,7 +16017,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Gain on forgiven interest on debt [note 8]</t>
+          <t>Change in non-cash working capital [note 17]</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -16115,18 +16041,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="5" t="n">
-        <v>-16.084062</v>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="n">
+        <v>-0.739698</v>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>-0.187861</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -16152,15 +16076,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligations [note 9]</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Additions to property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -16176,16 +16104,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H161" s="5" t="n">
-        <v>0.020644</v>
-      </c>
-      <c r="I161" s="5" t="n">
-        <v>0.02142</v>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>-0.005715</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -16216,17 +16146,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Decrease in cash</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ChangeInWorkingCapital</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -16244,21 +16174,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H162" s="5" t="n">
-        <v>-1.0247</v>
-      </c>
-      <c r="I162" s="5" t="n">
-        <v>-1.317615</v>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>-1.313789</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>-0.525441</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -16284,17 +16214,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -16312,21 +16242,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H163" s="5" t="n">
-        <v>-0.210826</v>
-      </c>
-      <c r="I163" s="5" t="n">
-        <v>-0.013852</v>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>3.64744</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>2.333651</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -16357,12 +16287,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Purchase of property, plant and equipment [note 7]</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -16380,23 +16310,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H164" s="5" t="n">
-        <v>-0.001413</v>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J164" s="5" t="n">
+        <v>2.333651</v>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>1.80821</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -16422,19 +16350,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Net income (loss) and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -16445,16 +16369,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G165" s="5" t="n">
-        <v>-0.004129</v>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H165" s="5" t="n">
-        <v>-0.001413</v>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.408696</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>13.495571</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -16490,39 +16414,33 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>0.034507</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>0.658626</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>1.594738</v>
       </c>
       <c r="H166" s="5" t="n">
-        <v>-0.212239</v>
+        <v>1.201926</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>-0.013852</v>
+        <v>0.8601259999999999</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -16558,37 +16476,35 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Impairment</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G167" s="5" t="n">
-        <v>0.26893</v>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>0.278357</v>
+      <c r="F167" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I167" s="5" t="n">
-        <v>0.066118</v>
+        <v>3.010705</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -16624,19 +16540,15 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Gain on forgiven interest on debt [note 8]</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -16647,14 +16559,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G168" s="5" t="n">
-        <v>0.278357</v>
-      </c>
-      <c r="H168" s="5" t="n">
-        <v>0.066118</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I168" s="5" t="n">
-        <v>0.052266</v>
+        <v>-16.084062</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -16695,28 +16611,30 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Accrued interest on notes payable [note 9]</t>
+          <t>Accretion of asset retirement obligations [note 9]</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" s="5" t="n">
-        <v>2.627131</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>2.967536</v>
-      </c>
-      <c r="G169" s="5" t="n">
-        <v>3.842095</v>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>0.020644</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>0.02142</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -16757,26 +16675,34 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital [note 16]</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" s="5" t="n">
-        <v>0.14733</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>0.487545</v>
-      </c>
-      <c r="G170" s="5" t="n">
-        <v>0.066416</v>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H170" s="5" t="n">
         <v>-1.0247</v>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I170" s="5" t="n">
+        <v>-1.317615</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -16817,10 +16743,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Cash flows provided by (used in) operating activities</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -16831,16 +16761,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G171" s="5" t="n">
-        <v>0.013556</v>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H171" s="5" t="n">
         <v>-0.210826</v>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I171" s="5" t="n">
+        <v>-0.013852</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -16881,7 +16811,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Purchase of property, plant and equipment [note 8]</t>
+          <t>Purchase of property, plant and equipment [note 7]</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -16889,14 +16819,20 @@
           <t>PurchaseOfPPE</t>
         </is>
       </c>
-      <c r="E172" s="5" t="n">
-        <v>-0.025614</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>-0.019723</v>
-      </c>
-      <c r="G172" s="5" t="n">
-        <v>-0.004129</v>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H172" s="5" t="n">
         <v>-0.001413</v>
@@ -16945,12 +16881,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>(Decrease) increase in cash and cash equivalents</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -16964,10 +16900,10 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.009427</v>
+        <v>-0.004129</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>-0.212239</v>
+        <v>-0.001413</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -17008,39 +16944,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Decrease in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="n">
-        <v>-3.755</v>
-      </c>
-      <c r="F174" s="5" t="n">
-        <v>-9.242405</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H174" s="5" t="n">
+        <v>-0.212239</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>-0.013852</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -17081,34 +17017,32 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES total</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="n">
-        <v>-0.025614</v>
-      </c>
-      <c r="F175" s="5" t="n">
-        <v>-0.019723</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>0.278357</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>0.066118</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -17144,37 +17078,37 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Repayment of financing liability</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" s="5" t="n">
-        <v>-0.009431</v>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G176" s="5" t="n">
+        <v>0.278357</v>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>0.066118</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>0.052266</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -17210,25 +17144,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Increase in notes payable [note 9]</t>
+          <t>Accrued interest on notes payable [note 9]</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" s="5" t="n">
-        <v>0.593413</v>
+        <v>2.627131</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.967536</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>3.842095</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -17274,34 +17206,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES total</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Change in non-cash working capital [note 16]</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" s="5" t="n">
-        <v>0.583982</v>
+        <v>0.14733</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.487545</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.066416</v>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>-1.0247</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -17342,34 +17266,30 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="n">
-        <v>-0.37464</v>
-      </c>
-      <c r="F179" s="5" t="n">
-        <v>0.165123</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows provided by (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.013556</v>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>-0.210826</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -17410,34 +17330,30 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Purchase of property, plant and equipment [note 8]</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>0.397027</v>
+        <v>-0.025614</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>0.022387</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019723</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>-0.004129</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>-0.001413</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -17478,61 +17394,599 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>(Decrease) increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.009427</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>-0.212239</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>-3.755</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>-9.242405</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES total</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>-0.025614</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>-0.019723</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
           <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Repayment of financing liability</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" s="5" t="n">
+        <v>-0.009431</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Increase in notes payable [note 9]</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" s="5" t="n">
+        <v>0.593413</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES total</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>0.583982</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n">
+        <v>-0.37464</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>0.165123</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>0.397027</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>0.022387</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
         <is>
           <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E181" s="5" t="n">
+      <c r="E189" s="5" t="n">
         <v>0.022387</v>
       </c>
-      <c r="F181" s="5" t="n">
+      <c r="F189" s="5" t="n">
         <v>0.18751</v>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
